--- a/tests/e2e/fixtures/tanah-import-run.xlsx
+++ b/tests/e2e/fixtures/tanah-import-run.xlsx
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>940339</v>
+        <v>927730</v>
       </c>
       <c r="G7" t="s">
         <v>5</v>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>840339</v>
+        <v>827730</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -484,7 +484,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>740339</v>
+        <v>727730</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>

--- a/tests/e2e/fixtures/tanah-import-run.xlsx
+++ b/tests/e2e/fixtures/tanah-import-run.xlsx
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>927730</v>
+        <v>939814</v>
       </c>
       <c r="G7" t="s">
         <v>5</v>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>827730</v>
+        <v>839814</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -484,7 +484,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>727730</v>
+        <v>739814</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
